--- a/tests/test_data/game_config.xlsx
+++ b/tests/test_data/game_config.xlsx
@@ -521,7 +521,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
@@ -555,7 +555,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -623,7 +623,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F6" t="n">
         <v>8</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>

--- a/tests/test_data/game_config.xlsx
+++ b/tests/test_data/game_config.xlsx
@@ -521,7 +521,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
@@ -555,7 +555,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -623,7 +623,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F6" t="n">
         <v>8</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
